--- a/epsilon-phi-core/src/Scripts/Case Studies/3. Single Stock Analysis/Single Stock Analysis.xlsx
+++ b/epsilon-phi-core/src/Scripts/Case Studies/3. Single Stock Analysis/Single Stock Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/Repositories/Python/epsilon-phi/epsilon-phi-core/src/Scripts/Case Studies/3. Single Stock Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F606F898-475D-244B-A3D4-B6B3CE12B99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15037DC0-C700-004E-A112-C2B720A572F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3140" yWindow="800" windowWidth="44720" windowHeight="25300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -434,17 +434,7 @@
 (Undiversifiable)</t>
   </si>
   <si>
-    <r>
-      <t>Implied Return</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>1</t>
-    </r>
+    <t>Implied Return</t>
   </si>
 </sst>
 </file>
@@ -455,7 +445,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -526,11 +516,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri (Body)"/>
     </font>
   </fonts>
   <fills count="8">
@@ -969,19 +954,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2259,7 +2244,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E96C2859-22A6-BE48-B221-C9D4C2487CB7}" type="CELLRANGE">
+                    <a:fld id="{65E7055D-F7CB-A740-89B6-177043742251}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2292,7 +2277,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{85ED0B37-9945-E046-B18F-B620C6E54A22}" type="CELLRANGE">
+                    <a:fld id="{5DF3B80B-3F27-EA4C-BEB3-9D15F47CAFA4}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2401,7 +2386,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{55024684-5950-EE43-9632-AE7323FA7732}" type="CELLRANGE">
+                    <a:fld id="{132DEE7E-6183-1E44-8ABD-B49F6B804EDF}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2434,7 +2419,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A2FF8E42-46C7-384D-B6F3-64D64F49FB80}" type="CELLRANGE">
+                    <a:fld id="{18544626-F37D-F343-89CC-AFF64405B32C}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2467,7 +2452,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2BB2CB40-DADB-2140-A2F1-E241A6B16252}" type="CELLRANGE">
+                    <a:fld id="{A0DE2D0B-95C8-0C44-8670-C6A7A9680AEE}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3477,7 +3462,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F0AF5EB8-29DC-474D-927E-0DC8FC0C481F}" type="CELLRANGE">
+                    <a:fld id="{893C7303-20F4-2747-B7ED-0BD8E8FEBED2}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -20176,7 +20161,7 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Implied Return1</c:v>
+                  <c:v>Implied Return</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Risk Premia</c:v>
@@ -20336,7 +20321,7 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Implied Return1</c:v>
+                  <c:v>Implied Return</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Risk Premia</c:v>
@@ -28319,13 +28304,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.5" customWidth="1"/>
     <col min="2" max="5" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="37" customHeight="1">
       <c r="A1" s="46"/>
       <c r="B1" s="47" t="s">
         <v>1</v>
@@ -28340,7 +28325,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="17" customHeight="1">
       <c r="A2" s="49" t="s">
         <v>5</v>
       </c>
@@ -28357,7 +28342,7 @@
         <v>0.20499999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="17" customHeight="1">
       <c r="A3" s="51" t="s">
         <v>6</v>
       </c>
@@ -28374,7 +28359,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="17" customHeight="1">
       <c r="A4" s="51" t="s">
         <v>7</v>
       </c>
@@ -28391,7 +28376,7 @@
         <v>6.0000000000000009</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="17" customHeight="1">
       <c r="A5" s="49" t="s">
         <v>8</v>
       </c>
@@ -28408,7 +28393,7 @@
         <v>7.0000000000000021E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="17" customHeight="1">
       <c r="A6" s="51" t="s">
         <v>9</v>
       </c>
@@ -28425,7 +28410,7 @@
         <v>7.0000000000000018</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="17" customHeight="1">
       <c r="A7" s="49" t="s">
         <v>10</v>
       </c>
@@ -28442,7 +28427,7 @@
         <v>0.65900000000000014</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="17" customHeight="1">
       <c r="A8" s="51" t="s">
         <v>11</v>
       </c>
@@ -28459,7 +28444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="17" customHeight="1">
       <c r="A9" s="51" t="s">
         <v>12</v>
       </c>
@@ -28476,7 +28461,7 @@
         <v>18.530297029702972</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="17" customHeight="1">
       <c r="A10" s="51" t="s">
         <v>13</v>
       </c>
@@ -28493,7 +28478,7 @@
         <v>20.748712871287129</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="17" customHeight="1">
       <c r="A11" s="51" t="s">
         <v>14</v>
       </c>
@@ -28510,7 +28495,7 @@
         <v>6.5247524752475261</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="17" customHeight="1">
       <c r="A12" s="51" t="s">
         <v>15</v>
       </c>
@@ -28527,7 +28512,7 @@
         <v>7.4382178217821799</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="17" customHeight="1">
       <c r="A13" s="51" t="s">
         <v>16</v>
       </c>
@@ -28544,7 +28529,7 @@
         <v>2.2184158415841591</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="17" customHeight="1">
       <c r="A14" s="51" t="s">
         <v>17</v>
       </c>
@@ -28561,7 +28546,7 @@
         <v>3.3928712871287132</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="17" customHeight="1">
       <c r="A15" s="51" t="s">
         <v>18</v>
       </c>
@@ -28578,7 +28563,7 @@
         <v>1.6964356435643571</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="17" customHeight="1">
       <c r="A16" s="51" t="s">
         <v>19</v>
       </c>
@@ -28595,7 +28580,7 @@
         <v>1.6964356435643571</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="17" customHeight="1">
       <c r="A17" s="51" t="s">
         <v>20</v>
       </c>
@@ -28612,7 +28597,7 @@
         <v>1.826930693069307</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="17" customHeight="1">
       <c r="A18" s="51" t="s">
         <v>21</v>
       </c>
@@ -28629,7 +28614,7 @@
         <v>1.826930693069307</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="17" customHeight="1">
       <c r="A19" s="49" t="s">
         <v>22</v>
       </c>
@@ -28646,7 +28631,7 @@
         <v>6.6000000000000017E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="17" customHeight="1">
       <c r="A20" s="51" t="s">
         <v>23</v>
       </c>
@@ -28663,7 +28648,7 @@
         <v>0.66000000000000014</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="17" customHeight="1">
       <c r="A21" s="51" t="s">
         <v>24</v>
       </c>
@@ -28680,7 +28665,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="17" customHeight="1">
       <c r="A22" s="51" t="s">
         <v>25</v>
       </c>
@@ -28697,7 +28682,7 @@
         <v>3.9600000000000009</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="17" customHeight="1">
       <c r="A23" s="49" t="s">
         <v>26</v>
       </c>
@@ -28714,7 +28699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="17" customHeight="1">
       <c r="A24" s="51" t="s">
         <v>27</v>
       </c>
@@ -28731,7 +28716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="23" customHeight="1">
       <c r="A25" s="53" t="s">
         <v>28</v>
       </c>
@@ -28748,7 +28733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="3" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="3" customHeight="1">
       <c r="A26" s="55"/>
       <c r="B26" s="5">
         <v>0</v>
@@ -28763,7 +28748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="23" customHeight="1">
       <c r="A27" s="57" t="s">
         <v>29</v>
       </c>
@@ -28780,7 +28765,7 @@
         <v>6.6940349344910069E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="23" customHeight="1">
       <c r="A28" s="57" t="s">
         <v>30</v>
       </c>
@@ -28797,7 +28782,7 @@
         <v>0.4241353698624088</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="3" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="3" customHeight="1">
       <c r="A29" s="55"/>
       <c r="B29" s="5">
         <v>0</v>
@@ -28812,7 +28797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="23" customHeight="1">
       <c r="A30" s="60" t="s">
         <v>31</v>
       </c>
@@ -28837,14 +28822,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E65B17-ACC8-4343-95EB-5E46D2E41740}">
   <dimension ref="A1:R58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" style="71" bestFit="1" customWidth="1"/>
     <col min="3" max="7" width="10.83203125" style="71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18">
       <c r="A1" s="1"/>
       <c r="B1" s="72" t="s">
         <v>106</v>
@@ -28876,7 +28861,7 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
         <v>103</v>
       </c>
@@ -28917,7 +28902,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
         <v>113</v>
       </c>
@@ -28958,7 +28943,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
         <v>104</v>
       </c>
@@ -28999,7 +28984,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18">
       <c r="A5" s="1" t="s">
         <v>105</v>
       </c>
@@ -29040,7 +29025,7 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" hidden="1">
       <c r="A6" s="1" t="s">
         <v>114</v>
       </c>
@@ -29081,7 +29066,7 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
         <v>125</v>
       </c>
@@ -29122,7 +29107,7 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18">
       <c r="A8" s="1" t="s">
         <v>115</v>
       </c>
@@ -29163,7 +29148,7 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
         <v>116</v>
       </c>
@@ -29204,7 +29189,7 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" hidden="1">
       <c r="A10" s="1" t="s">
         <v>117</v>
       </c>
@@ -29245,7 +29230,7 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
         <v>118</v>
       </c>
@@ -29286,7 +29271,7 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" hidden="1">
       <c r="A12" s="1" t="s">
         <v>119</v>
       </c>
@@ -29327,7 +29312,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
         <v>120</v>
       </c>
@@ -29368,7 +29353,7 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18">
       <c r="A14" s="1" t="s">
         <v>93</v>
       </c>
@@ -29409,7 +29394,7 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" hidden="1">
       <c r="A15" s="1" t="s">
         <v>94</v>
       </c>
@@ -29450,7 +29435,7 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18">
       <c r="A16" s="1" t="s">
         <v>121</v>
       </c>
@@ -29491,7 +29476,7 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18">
       <c r="A17" s="1" t="s">
         <v>122</v>
       </c>
@@ -29532,7 +29517,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18">
       <c r="A18" s="1" t="s">
         <v>95</v>
       </c>
@@ -29573,7 +29558,7 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18">
       <c r="A19" s="1" t="s">
         <v>102</v>
       </c>
@@ -29613,7 +29598,7 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18">
       <c r="A20" s="1" t="s">
         <v>96</v>
       </c>
@@ -29654,7 +29639,7 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18">
       <c r="A21" s="1" t="s">
         <v>97</v>
       </c>
@@ -29695,7 +29680,7 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18">
       <c r="A22" s="1" t="s">
         <v>98</v>
       </c>
@@ -29736,7 +29721,7 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18">
       <c r="A23" s="1" t="s">
         <v>99</v>
       </c>
@@ -29777,7 +29762,7 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18">
       <c r="A24" s="1" t="s">
         <v>100</v>
       </c>
@@ -29818,7 +29803,7 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18">
       <c r="A25" s="1" t="s">
         <v>101</v>
       </c>
@@ -29859,7 +29844,7 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18">
       <c r="A26" s="1" t="s">
         <v>120</v>
       </c>
@@ -29900,7 +29885,7 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" hidden="1">
       <c r="A27" s="1" t="s">
         <v>123</v>
       </c>
@@ -29941,7 +29926,7 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18">
       <c r="A28" s="1" t="s">
         <v>124</v>
       </c>
@@ -29982,7 +29967,7 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18">
       <c r="A29" s="1" t="s">
         <v>108</v>
       </c>
@@ -30023,7 +30008,7 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18">
       <c r="A30" s="1"/>
       <c r="B30" s="72"/>
       <c r="C30" s="72"/>
@@ -30043,7 +30028,7 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18">
       <c r="A31" s="1"/>
       <c r="B31" s="72"/>
       <c r="C31" s="72"/>
@@ -30063,7 +30048,7 @@
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18">
       <c r="A32" s="1"/>
       <c r="B32" s="72"/>
       <c r="C32" s="72"/>
@@ -30083,7 +30068,7 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18">
       <c r="A33" s="1"/>
       <c r="B33" s="72"/>
       <c r="C33" s="72"/>
@@ -30103,7 +30088,7 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18">
       <c r="A34" s="1"/>
       <c r="B34" s="72"/>
       <c r="C34" s="72"/>
@@ -30123,7 +30108,7 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18">
       <c r="A35" s="1"/>
       <c r="B35" s="72"/>
       <c r="C35" s="72"/>
@@ -30143,7 +30128,7 @@
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18">
       <c r="A36" s="1"/>
       <c r="B36" s="72"/>
       <c r="C36" s="72"/>
@@ -30163,7 +30148,7 @@
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18">
       <c r="A37" s="1"/>
       <c r="B37" s="72"/>
       <c r="C37" s="72"/>
@@ -30183,7 +30168,7 @@
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18">
       <c r="A38" s="1"/>
       <c r="B38" s="72"/>
       <c r="C38" s="72"/>
@@ -30203,7 +30188,7 @@
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18">
       <c r="A39" s="1"/>
       <c r="B39" s="72"/>
       <c r="C39" s="72"/>
@@ -30215,7 +30200,7 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18">
       <c r="A40" s="1"/>
       <c r="B40" s="72"/>
       <c r="C40" s="72"/>
@@ -30227,7 +30212,7 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18">
       <c r="A41" s="1"/>
       <c r="B41" s="72"/>
       <c r="C41" s="72"/>
@@ -30239,7 +30224,7 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18">
       <c r="A42" s="1"/>
       <c r="B42" s="72"/>
       <c r="C42" s="72"/>
@@ -30251,7 +30236,7 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18">
       <c r="A43" s="1"/>
       <c r="B43" s="72"/>
       <c r="C43" s="72"/>
@@ -30263,7 +30248,7 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18">
       <c r="A44" s="1"/>
       <c r="B44" s="72"/>
       <c r="C44" s="72"/>
@@ -30275,7 +30260,7 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18">
       <c r="A45" s="1"/>
       <c r="B45" s="72"/>
       <c r="C45" s="72"/>
@@ -30287,7 +30272,7 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18">
       <c r="A46" s="1"/>
       <c r="B46" s="72"/>
       <c r="C46" s="72"/>
@@ -30299,7 +30284,7 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18">
       <c r="A47" s="1"/>
       <c r="B47" s="72"/>
       <c r="C47" s="72"/>
@@ -30311,7 +30296,7 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18">
       <c r="A48" s="1"/>
       <c r="B48" s="72"/>
       <c r="C48" s="72"/>
@@ -30323,7 +30308,7 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10">
       <c r="A49" s="1"/>
       <c r="B49" s="72"/>
       <c r="C49" s="72"/>
@@ -30335,7 +30320,7 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10">
       <c r="A50" s="1"/>
       <c r="B50" s="72"/>
       <c r="C50" s="72"/>
@@ -30347,7 +30332,7 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10">
       <c r="A51" s="1"/>
       <c r="B51" s="72"/>
       <c r="C51" s="72"/>
@@ -30359,7 +30344,7 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10">
       <c r="A52" s="1"/>
       <c r="B52" s="72"/>
       <c r="C52" s="72"/>
@@ -30371,7 +30356,7 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10">
       <c r="A53" s="1"/>
       <c r="B53" s="72"/>
       <c r="C53" s="72"/>
@@ -30383,7 +30368,7 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10">
       <c r="A54" s="1"/>
       <c r="B54" s="72"/>
       <c r="C54" s="72"/>
@@ -30395,7 +30380,7 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10">
       <c r="A55" s="1"/>
       <c r="B55" s="72"/>
       <c r="C55" s="72"/>
@@ -30407,7 +30392,7 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10">
       <c r="A56" s="1"/>
       <c r="B56" s="72"/>
       <c r="C56" s="72"/>
@@ -30419,7 +30404,7 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10">
       <c r="A57" s="1"/>
       <c r="B57" s="72"/>
       <c r="C57" s="72"/>
@@ -30431,7 +30416,7 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10">
       <c r="A58" s="1"/>
       <c r="B58" s="72"/>
       <c r="C58" s="72"/>
@@ -30457,161 +30442,161 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S95"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="35" customHeight="1">
       <c r="A1" s="8"/>
-      <c r="B1" s="76" t="s">
+      <c r="B1" s="81" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="77"/>
-      <c r="D1" s="76" t="s">
+      <c r="D1" s="81" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="77"/>
-      <c r="F1" s="76" t="s">
+      <c r="F1" s="81" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="77"/>
-      <c r="H1" s="76" t="s">
+      <c r="H1" s="81" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="77"/>
-      <c r="J1" s="76" t="s">
+      <c r="J1" s="81" t="s">
         <v>4</v>
       </c>
       <c r="K1" s="77"/>
     </row>
-    <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="20" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="78">
+      <c r="B2" s="76">
         <v>0.55000000000000004</v>
       </c>
       <c r="C2" s="77"/>
-      <c r="D2" s="78">
+      <c r="D2" s="76">
         <v>0.22</v>
       </c>
       <c r="E2" s="77"/>
-      <c r="F2" s="78">
+      <c r="F2" s="76">
         <v>0.62</v>
       </c>
       <c r="G2" s="77"/>
-      <c r="H2" s="78">
+      <c r="H2" s="76">
         <v>0.40500000000000003</v>
       </c>
       <c r="I2" s="77"/>
-      <c r="J2" s="78">
+      <c r="J2" s="76">
         <v>0.20499999999999999</v>
       </c>
       <c r="K2" s="77"/>
     </row>
-    <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="16" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="78">
+      <c r="B3" s="76">
         <v>0</v>
       </c>
       <c r="C3" s="77"/>
-      <c r="D3" s="78">
+      <c r="D3" s="76">
         <v>0</v>
       </c>
       <c r="E3" s="77"/>
-      <c r="F3" s="78">
+      <c r="F3" s="76">
         <v>0.05</v>
       </c>
       <c r="G3" s="77"/>
-      <c r="H3" s="78">
+      <c r="H3" s="76">
         <v>0.06</v>
       </c>
       <c r="I3" s="77"/>
-      <c r="J3" s="78">
+      <c r="J3" s="76">
         <v>7.0000000000000021E-2</v>
       </c>
       <c r="K3" s="77"/>
     </row>
-    <row r="4" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="16" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="78">
+      <c r="B4" s="76">
         <v>0.31499999999999989</v>
       </c>
       <c r="C4" s="77"/>
-      <c r="D4" s="78">
+      <c r="D4" s="76">
         <v>0.126</v>
       </c>
       <c r="E4" s="77"/>
-      <c r="F4" s="78">
+      <c r="F4" s="76">
         <v>0.28999999999999998</v>
       </c>
       <c r="G4" s="77"/>
-      <c r="H4" s="78">
+      <c r="H4" s="76">
         <v>0.48500000000000021</v>
       </c>
       <c r="I4" s="77"/>
-      <c r="J4" s="78">
+      <c r="J4" s="76">
         <v>0.65900000000000014</v>
       </c>
       <c r="K4" s="77"/>
     </row>
-    <row r="5" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="16" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="78">
+      <c r="B5" s="76">
         <v>0.13500000000000001</v>
       </c>
       <c r="C5" s="77"/>
-      <c r="D5" s="78">
+      <c r="D5" s="76">
         <v>5.3999999999999992E-2</v>
       </c>
       <c r="E5" s="77"/>
-      <c r="F5" s="78">
+      <c r="F5" s="76">
         <v>0.04</v>
       </c>
       <c r="G5" s="77"/>
-      <c r="H5" s="78">
+      <c r="H5" s="76">
         <v>0.05</v>
       </c>
       <c r="I5" s="77"/>
-      <c r="J5" s="78">
+      <c r="J5" s="76">
         <v>6.6000000000000017E-2</v>
       </c>
       <c r="K5" s="77"/>
     </row>
-    <row r="6" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="16" customHeight="1">
       <c r="A6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="78">
+      <c r="B6" s="76">
         <v>0</v>
       </c>
       <c r="C6" s="77"/>
-      <c r="D6" s="78">
+      <c r="D6" s="76">
         <v>0.6</v>
       </c>
       <c r="E6" s="77"/>
-      <c r="F6" s="78">
+      <c r="F6" s="76">
         <v>0</v>
       </c>
       <c r="G6" s="77"/>
-      <c r="H6" s="78">
+      <c r="H6" s="76">
         <v>0</v>
       </c>
       <c r="I6" s="77"/>
-      <c r="J6" s="78">
+      <c r="J6" s="76">
         <v>0</v>
       </c>
       <c r="K6" s="77"/>
     </row>
-    <row r="7" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="16" customHeight="1">
       <c r="A7" s="12" t="s">
         <v>29</v>
       </c>
@@ -30636,57 +30621,57 @@
       </c>
       <c r="K7" s="80"/>
     </row>
-    <row r="8" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="16" customHeight="1">
       <c r="A8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="81">
+      <c r="B8" s="78">
         <v>0.43815452717638198</v>
       </c>
       <c r="C8" s="77"/>
-      <c r="D8" s="81">
+      <c r="D8" s="78">
         <v>0.16346605152076499</v>
       </c>
       <c r="E8" s="77"/>
-      <c r="F8" s="81">
+      <c r="F8" s="78">
         <v>0.53400855024113281</v>
       </c>
       <c r="G8" s="77"/>
-      <c r="H8" s="81">
+      <c r="H8" s="78">
         <v>0.46413636396119312</v>
       </c>
       <c r="I8" s="77"/>
-      <c r="J8" s="81">
+      <c r="J8" s="78">
         <v>0.4241353698624088</v>
       </c>
       <c r="K8" s="77"/>
     </row>
-    <row r="9" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="16" customHeight="1">
       <c r="A9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="78">
+      <c r="B9" s="76">
         <v>5.7324245809806711E-2</v>
       </c>
       <c r="C9" s="77"/>
-      <c r="D9" s="78">
+      <c r="D9" s="76">
         <v>0.22530577018721809</v>
       </c>
       <c r="E9" s="77"/>
-      <c r="F9" s="78">
+      <c r="F9" s="76">
         <v>4.9650061770962158E-2</v>
       </c>
       <c r="G9" s="77"/>
-      <c r="H9" s="78">
+      <c r="H9" s="76">
         <v>7.4615293576842989E-2</v>
       </c>
       <c r="I9" s="77"/>
-      <c r="J9" s="78">
+      <c r="J9" s="76">
         <v>9.8884347604670852E-2</v>
       </c>
       <c r="K9" s="77"/>
     </row>
-    <row r="10" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="16" customHeight="1">
       <c r="A10" s="8" t="s">
         <v>32</v>
       </c>
@@ -30701,7 +30686,7 @@
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="16" customHeight="1">
       <c r="A11" s="13" t="s">
         <v>33</v>
       </c>
@@ -30736,7 +30721,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="20" customHeight="1">
       <c r="A12" s="15" t="s">
         <v>36</v>
       </c>
@@ -30771,7 +30756,7 @@
         <v>0.1441289309290876</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="16" customHeight="1">
       <c r="A13" s="15" t="s">
         <v>37</v>
       </c>
@@ -30806,7 +30791,7 @@
         <v>-0.36676307923825863</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="16" customHeight="1">
       <c r="A14" s="15" t="s">
         <v>38</v>
       </c>
@@ -30841,7 +30826,7 @@
         <v>-6.449751766232692E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="16" customHeight="1">
       <c r="A15" s="15" t="s">
         <v>39</v>
       </c>
@@ -30876,7 +30861,7 @@
         <v>-0.14155468815168179</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="16" customHeight="1">
       <c r="A16" s="15" t="s">
         <v>40</v>
       </c>
@@ -30911,7 +30896,7 @@
         <v>-0.14337964987589841</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="16" customHeight="1">
       <c r="A17" s="15" t="s">
         <v>41</v>
       </c>
@@ -30946,7 +30931,7 @@
         <v>-6.3945054481720276E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="16" customHeight="1">
       <c r="A18" s="15" t="s">
         <v>42</v>
       </c>
@@ -30981,7 +30966,7 @@
         <v>-0.10372780578272631</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="16" customHeight="1">
       <c r="A19" s="15" t="s">
         <v>43</v>
       </c>
@@ -31016,7 +31001,7 @@
         <v>-0.29282898647372851</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="16" customHeight="1">
       <c r="A20" s="15" t="s">
         <v>44</v>
       </c>
@@ -31051,7 +31036,7 @@
         <v>-0.37816467439412388</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="16" customHeight="1">
       <c r="A21" s="15" t="s">
         <v>45</v>
       </c>
@@ -31086,7 +31071,7 @@
         <v>-0.1344414265931313</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="16" customHeight="1">
       <c r="A22" s="13" t="s">
         <v>46</v>
       </c>
@@ -31101,7 +31086,7 @@
       <c r="J22" s="14"/>
       <c r="K22" s="14"/>
     </row>
-    <row r="23" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="16" customHeight="1">
       <c r="A23" s="15" t="s">
         <v>47</v>
       </c>
@@ -31136,7 +31121,7 @@
         <v>7.6409858682636389E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="16" customHeight="1">
       <c r="A24" s="15" t="s">
         <v>48</v>
       </c>
@@ -31171,7 +31156,7 @@
         <v>0.25139086015100037</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="16" customHeight="1">
       <c r="A25" s="15" t="s">
         <v>49</v>
       </c>
@@ -31206,7 +31191,7 @@
         <v>0.31791022087462562</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="16" customHeight="1">
       <c r="A26" s="13" t="s">
         <v>50</v>
       </c>
@@ -31221,7 +31206,7 @@
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
     </row>
-    <row r="27" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="16" customHeight="1">
       <c r="A27" s="15" t="s">
         <v>47</v>
       </c>
@@ -31256,7 +31241,7 @@
         <v>0.1046827476364089</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="16" customHeight="1">
       <c r="A28" s="15" t="s">
         <v>48</v>
       </c>
@@ -31291,7 +31276,7 @@
         <v>0.29401706099260139</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="16" customHeight="1">
       <c r="A29" s="15" t="s">
         <v>49</v>
       </c>
@@ -31326,7 +31311,7 @@
         <v>0.37069194754087231</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="16" customHeight="1">
       <c r="A30" s="13" t="s">
         <v>51</v>
       </c>
@@ -31341,7 +31326,7 @@
       <c r="J30" s="14"/>
       <c r="K30" s="14"/>
     </row>
-    <row r="31" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" ht="16" customHeight="1">
       <c r="A31" s="15" t="s">
         <v>47</v>
       </c>
@@ -31376,7 +31361,7 @@
         <v>0.38190000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="16" customHeight="1">
       <c r="A32" s="15" t="s">
         <v>48</v>
       </c>
@@ -31411,7 +31396,7 @@
         <v>0.27489999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" ht="16" customHeight="1">
       <c r="A33" s="15" t="s">
         <v>49</v>
       </c>
@@ -31446,7 +31431,7 @@
         <v>0.20569999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:19" ht="16" customHeight="1">
       <c r="A34" s="8" t="s">
         <v>52</v>
       </c>
@@ -31461,7 +31446,7 @@
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
     </row>
-    <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:19" ht="16" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -31482,7 +31467,7 @@
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
     </row>
-    <row r="36" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:19" ht="20" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -31503,7 +31488,7 @@
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -31524,7 +31509,7 @@
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
         <v>89</v>
@@ -31549,7 +31534,7 @@
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19">
       <c r="A39" s="63" t="s">
         <v>86</v>
       </c>
@@ -31581,7 +31566,7 @@
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19">
       <c r="A40" s="63" t="s">
         <v>87</v>
       </c>
@@ -31613,7 +31598,7 @@
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19">
       <c r="A41" s="63" t="s">
         <v>88</v>
       </c>
@@ -31645,7 +31630,7 @@
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:19">
       <c r="A42" s="63" t="s">
         <v>86</v>
       </c>
@@ -31677,7 +31662,7 @@
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:19">
       <c r="A43" s="63" t="s">
         <v>87</v>
       </c>
@@ -31709,7 +31694,7 @@
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:19">
       <c r="A44" s="63" t="s">
         <v>88</v>
       </c>
@@ -31741,7 +31726,7 @@
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -31762,7 +31747,7 @@
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:19">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -31783,7 +31768,7 @@
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:19">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -31804,7 +31789,7 @@
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:19">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -31825,7 +31810,7 @@
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:19">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -31846,7 +31831,7 @@
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:19">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -31867,7 +31852,7 @@
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:19">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -31888,7 +31873,7 @@
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:19">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -31909,7 +31894,7 @@
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:19">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -31930,7 +31915,7 @@
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:19">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -31951,7 +31936,7 @@
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:19">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -31972,7 +31957,7 @@
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:19">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -31993,7 +31978,7 @@
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:19">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -32014,7 +31999,7 @@
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:19">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -32035,7 +32020,7 @@
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:19">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -32056,7 +32041,7 @@
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:19">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -32077,7 +32062,7 @@
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:19">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -32098,7 +32083,7 @@
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:19">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -32119,7 +32104,7 @@
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:19">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -32140,7 +32125,7 @@
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:19">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -32161,7 +32146,7 @@
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
     </row>
-    <row r="65" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:19" ht="32">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="74" t="s">
@@ -32187,7 +32172,7 @@
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
     </row>
-    <row r="66" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:19" ht="32">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="74" t="s">
@@ -32212,7 +32197,7 @@
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:19">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -32233,7 +32218,7 @@
       <c r="R67" s="1"/>
       <c r="S67" s="1"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:19">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -32254,7 +32239,7 @@
       <c r="R68" s="1"/>
       <c r="S68" s="1"/>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:19">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -32275,7 +32260,7 @@
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:19">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -32296,7 +32281,7 @@
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:19">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -32317,7 +32302,7 @@
       <c r="R71" s="1"/>
       <c r="S71" s="1"/>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:19">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -32338,7 +32323,7 @@
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:19">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -32359,7 +32344,7 @@
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:19">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -32380,7 +32365,7 @@
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:19">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -32401,7 +32386,7 @@
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:19">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -32422,7 +32407,7 @@
       <c r="R76" s="1"/>
       <c r="S76" s="1"/>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:19">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -32443,7 +32428,7 @@
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:19">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -32464,7 +32449,7 @@
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:19">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -32485,7 +32470,7 @@
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:19">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -32512,7 +32497,7 @@
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:19">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -32544,7 +32529,7 @@
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:19">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -32578,7 +32563,7 @@
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:19">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -32599,7 +32584,7 @@
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:19">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -32620,7 +32605,7 @@
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:19">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -32641,7 +32626,7 @@
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:19">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -32662,7 +32647,7 @@
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:19">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -32683,7 +32668,7 @@
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:19">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -32704,7 +32689,7 @@
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:19">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -32725,7 +32710,7 @@
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:19">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -32746,7 +32731,7 @@
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:19">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -32767,7 +32752,7 @@
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:19">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -32788,7 +32773,7 @@
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:19">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -32809,7 +32794,7 @@
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:19">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -32830,7 +32815,7 @@
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:19">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -32853,51 +32838,51 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="J9:K9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="B12:K21">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
@@ -32915,7 +32900,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="4" width="7" customWidth="1"/>
@@ -32926,7 +32911,7 @@
     <col min="9" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="16"/>
       <c r="B1" s="82" t="s">
         <v>53</v>
@@ -32942,7 +32927,7 @@
       </c>
       <c r="J1" s="83"/>
     </row>
-    <row r="2" spans="1:10" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="49" customHeight="1">
       <c r="A2" s="19"/>
       <c r="B2" s="84" t="s">
         <v>55</v>
@@ -32968,7 +32953,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="17" customHeight="1">
       <c r="A3" s="21" t="s">
         <v>5</v>
       </c>
@@ -32982,7 +32967,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="22"/>
     </row>
-    <row r="4" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="17" customHeight="1">
       <c r="A4" s="24" t="s">
         <v>60</v>
       </c>
@@ -33014,7 +32999,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="17" customHeight="1">
       <c r="A5" s="24" t="s">
         <v>61</v>
       </c>
@@ -33046,7 +33031,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="17" customHeight="1">
       <c r="A6" s="31" t="s">
         <v>8</v>
       </c>
@@ -33060,7 +33045,7 @@
       <c r="I6" s="37"/>
       <c r="J6" s="37"/>
     </row>
-    <row r="7" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="17" customHeight="1">
       <c r="A7" s="24" t="s">
         <v>62</v>
       </c>
@@ -33092,7 +33077,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="17" customHeight="1">
       <c r="A8" s="31" t="s">
         <v>10</v>
       </c>
@@ -33106,7 +33091,7 @@
       <c r="I8" s="37"/>
       <c r="J8" s="37"/>
     </row>
-    <row r="9" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="17" customHeight="1">
       <c r="A9" s="24" t="s">
         <v>63</v>
       </c>
@@ -33138,7 +33123,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="17" customHeight="1">
       <c r="A10" s="24" t="s">
         <v>64</v>
       </c>
@@ -33170,7 +33155,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="17" customHeight="1">
       <c r="A11" s="24" t="s">
         <v>65</v>
       </c>
@@ -33202,7 +33187,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="17" customHeight="1">
       <c r="A12" s="24" t="s">
         <v>66</v>
       </c>
@@ -33234,7 +33219,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="17" customHeight="1">
       <c r="A13" s="24" t="s">
         <v>67</v>
       </c>
@@ -33266,7 +33251,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="17" customHeight="1">
       <c r="A14" s="24" t="s">
         <v>68</v>
       </c>
@@ -33298,7 +33283,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="17" customHeight="1">
       <c r="A15" s="24" t="s">
         <v>69</v>
       </c>
@@ -33330,7 +33315,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="17" customHeight="1">
       <c r="A16" s="24" t="s">
         <v>70</v>
       </c>
@@ -33362,7 +33347,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="17" customHeight="1">
       <c r="A17" s="24" t="s">
         <v>71</v>
       </c>
@@ -33394,7 +33379,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="17" customHeight="1">
       <c r="A18" s="24" t="s">
         <v>72</v>
       </c>
@@ -33426,7 +33411,7 @@
         <v>44925</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="17" customHeight="1">
       <c r="A19" s="24" t="s">
         <v>73</v>
       </c>
@@ -33458,7 +33443,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="17" customHeight="1">
       <c r="A20" s="31" t="s">
         <v>22</v>
       </c>
@@ -33472,7 +33457,7 @@
       <c r="I20" s="37"/>
       <c r="J20" s="37"/>
     </row>
-    <row r="21" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="17" customHeight="1">
       <c r="A21" s="24" t="s">
         <v>74</v>
       </c>
@@ -33504,7 +33489,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="17" customHeight="1">
       <c r="A22" s="24" t="s">
         <v>75</v>
       </c>
@@ -33536,7 +33521,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="17" customHeight="1">
       <c r="A23" s="24" t="s">
         <v>76</v>
       </c>
@@ -33568,7 +33553,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="17" customHeight="1">
       <c r="A24" s="31" t="s">
         <v>26</v>
       </c>
@@ -33582,7 +33567,7 @@
       <c r="I24" s="37"/>
       <c r="J24" s="37"/>
     </row>
-    <row r="25" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="17" customHeight="1">
       <c r="A25" s="38" t="s">
         <v>77</v>
       </c>
@@ -33627,12 +33612,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17">
       <c r="A1" s="45"/>
       <c r="B1" s="75" t="s">
         <v>78</v>
@@ -33659,7 +33644,7 @@
       <c r="P1" s="45"/>
       <c r="Q1" s="45"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17">
       <c r="A2" s="45"/>
       <c r="B2" s="75" t="s">
         <v>82</v>
@@ -33686,7 +33671,7 @@
       <c r="P2" s="45"/>
       <c r="Q2" s="45"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17">
       <c r="A3" s="45">
         <v>0</v>
       </c>
@@ -33723,7 +33708,7 @@
       <c r="P3" s="45"/>
       <c r="Q3" s="45"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17">
       <c r="A4" s="45">
         <v>1</v>
       </c>
@@ -33760,7 +33745,7 @@
       <c r="P4" s="45"/>
       <c r="Q4" s="45"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17">
       <c r="A5" s="45">
         <v>2</v>
       </c>
@@ -33797,7 +33782,7 @@
       <c r="P5" s="45"/>
       <c r="Q5" s="45"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17">
       <c r="A6" s="45">
         <v>3</v>
       </c>
@@ -33834,7 +33819,7 @@
       <c r="P6" s="45"/>
       <c r="Q6" s="45"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17">
       <c r="A7" s="45">
         <v>4</v>
       </c>
@@ -33871,7 +33856,7 @@
       <c r="P7" s="45"/>
       <c r="Q7" s="45"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17">
       <c r="A8" s="45">
         <v>5</v>
       </c>
@@ -33908,7 +33893,7 @@
       <c r="P8" s="45"/>
       <c r="Q8" s="45"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17">
       <c r="A9" s="45">
         <v>6</v>
       </c>
@@ -33945,7 +33930,7 @@
       <c r="P9" s="45"/>
       <c r="Q9" s="45"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17">
       <c r="A10" s="45">
         <v>7</v>
       </c>
@@ -33982,7 +33967,7 @@
       <c r="P10" s="45"/>
       <c r="Q10" s="45"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17">
       <c r="A11" s="45">
         <v>8</v>
       </c>
@@ -34019,7 +34004,7 @@
       <c r="P11" s="45"/>
       <c r="Q11" s="45"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17">
       <c r="A12" s="45">
         <v>9</v>
       </c>
@@ -34056,7 +34041,7 @@
       <c r="P12" s="45"/>
       <c r="Q12" s="45"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17">
       <c r="A13" s="45">
         <v>10</v>
       </c>
@@ -34093,7 +34078,7 @@
       <c r="P13" s="45"/>
       <c r="Q13" s="45"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17">
       <c r="A14" s="45">
         <v>11</v>
       </c>
@@ -34130,7 +34115,7 @@
       <c r="P14" s="45"/>
       <c r="Q14" s="45"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17">
       <c r="A15" s="45">
         <v>12</v>
       </c>
@@ -34167,7 +34152,7 @@
       <c r="P15" s="45"/>
       <c r="Q15" s="45"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17">
       <c r="A16" s="45">
         <v>13</v>
       </c>
@@ -34204,7 +34189,7 @@
       <c r="P16" s="45"/>
       <c r="Q16" s="45"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17">
       <c r="A17" s="45">
         <v>14</v>
       </c>
@@ -34241,7 +34226,7 @@
       <c r="P17" s="45"/>
       <c r="Q17" s="45"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17">
       <c r="A18" s="45">
         <v>15</v>
       </c>
@@ -34278,7 +34263,7 @@
       <c r="P18" s="45"/>
       <c r="Q18" s="45"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17">
       <c r="A19" s="45">
         <v>16</v>
       </c>
@@ -34315,7 +34300,7 @@
       <c r="P19" s="45"/>
       <c r="Q19" s="45"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17">
       <c r="A20" s="45">
         <v>17</v>
       </c>
@@ -34352,7 +34337,7 @@
       <c r="P20" s="45"/>
       <c r="Q20" s="45"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17">
       <c r="A21" s="45">
         <v>18</v>
       </c>
@@ -34389,7 +34374,7 @@
       <c r="P21" s="45"/>
       <c r="Q21" s="45"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17">
       <c r="A22" s="45">
         <v>19</v>
       </c>
@@ -34426,7 +34411,7 @@
       <c r="P22" s="45"/>
       <c r="Q22" s="45"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17">
       <c r="A23" s="45">
         <v>20</v>
       </c>
@@ -34472,9 +34457,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17">
       <c r="A1" s="45"/>
       <c r="B1" s="45" t="s">
         <v>78</v>
@@ -34525,7 +34510,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17">
       <c r="A2" s="45"/>
       <c r="B2" s="45" t="s">
         <v>82</v>
@@ -34576,7 +34561,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17">
       <c r="A3" s="45">
         <v>0</v>
       </c>
@@ -34629,7 +34614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17">
       <c r="A4" s="45">
         <v>1</v>
       </c>
@@ -34682,7 +34667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17">
       <c r="A5" s="45">
         <v>2</v>
       </c>
@@ -34735,7 +34720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17">
       <c r="A6" s="45">
         <v>3</v>
       </c>
@@ -34788,7 +34773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17">
       <c r="A7" s="45">
         <v>4</v>
       </c>
@@ -34841,7 +34826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17">
       <c r="A8" s="45">
         <v>5</v>
       </c>
@@ -34894,7 +34879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17">
       <c r="A9" s="45">
         <v>6</v>
       </c>
@@ -34947,7 +34932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17">
       <c r="A10" s="45">
         <v>7</v>
       </c>
@@ -35000,7 +34985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17">
       <c r="A11" s="45">
         <v>8</v>
       </c>
@@ -35053,7 +35038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17">
       <c r="A12" s="45">
         <v>9</v>
       </c>
@@ -35106,7 +35091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17">
       <c r="A13" s="45">
         <v>10</v>
       </c>
@@ -35159,7 +35144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17">
       <c r="A14" s="45">
         <v>11</v>
       </c>
@@ -35212,7 +35197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17">
       <c r="A15" s="45">
         <v>12</v>
       </c>
@@ -35265,7 +35250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17">
       <c r="A16" s="45">
         <v>13</v>
       </c>
@@ -35318,7 +35303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17">
       <c r="A17" s="45">
         <v>14</v>
       </c>
@@ -35371,7 +35356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17">
       <c r="A18" s="45">
         <v>15</v>
       </c>
@@ -35424,7 +35409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17">
       <c r="A19" s="45">
         <v>16</v>
       </c>
@@ -35477,7 +35462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17">
       <c r="A20" s="45">
         <v>17</v>
       </c>
@@ -35530,7 +35515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17">
       <c r="A21" s="45">
         <v>18</v>
       </c>
@@ -35583,7 +35568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17">
       <c r="A22" s="45">
         <v>19</v>
       </c>
@@ -35636,7 +35621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17">
       <c r="A23" s="45">
         <v>20</v>
       </c>
@@ -35698,9 +35683,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Q23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17">
       <c r="A1" s="45"/>
       <c r="B1" s="45" t="s">
         <v>78</v>
@@ -35751,7 +35736,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17">
       <c r="A2" s="45"/>
       <c r="B2" s="45" t="s">
         <v>82</v>
@@ -35802,7 +35787,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17">
       <c r="A3" s="45">
         <v>0</v>
       </c>
@@ -35855,7 +35840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17">
       <c r="A4" s="45">
         <v>1</v>
       </c>
@@ -35908,7 +35893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17">
       <c r="A5" s="45">
         <v>2</v>
       </c>
@@ -35961,7 +35946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17">
       <c r="A6" s="45">
         <v>3</v>
       </c>
@@ -36014,7 +35999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17">
       <c r="A7" s="45">
         <v>4</v>
       </c>
@@ -36067,7 +36052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17">
       <c r="A8" s="45">
         <v>5</v>
       </c>
@@ -36120,7 +36105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17">
       <c r="A9" s="45">
         <v>6</v>
       </c>
@@ -36173,7 +36158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17">
       <c r="A10" s="45">
         <v>7</v>
       </c>
@@ -36226,7 +36211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17">
       <c r="A11" s="45">
         <v>8</v>
       </c>
@@ -36279,7 +36264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17">
       <c r="A12" s="45">
         <v>9</v>
       </c>
@@ -36332,7 +36317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17">
       <c r="A13" s="45">
         <v>10</v>
       </c>
@@ -36385,7 +36370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17">
       <c r="A14" s="45">
         <v>11</v>
       </c>
@@ -36438,7 +36423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17">
       <c r="A15" s="45">
         <v>12</v>
       </c>
@@ -36491,7 +36476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17">
       <c r="A16" s="45">
         <v>13</v>
       </c>
@@ -36544,7 +36529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17">
       <c r="A17" s="45">
         <v>14</v>
       </c>
@@ -36597,7 +36582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17">
       <c r="A18" s="45">
         <v>15</v>
       </c>
@@ -36650,7 +36635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17">
       <c r="A19" s="45">
         <v>16</v>
       </c>
@@ -36703,7 +36688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17">
       <c r="A20" s="45">
         <v>17</v>
       </c>
@@ -36756,7 +36741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17">
       <c r="A21" s="45">
         <v>18</v>
       </c>
@@ -36809,7 +36794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17">
       <c r="A22" s="45">
         <v>19</v>
       </c>
@@ -36862,7 +36847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17">
       <c r="A23" s="45">
         <v>20</v>
       </c>
@@ -36924,9 +36909,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:Q23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17">
       <c r="A1" s="45"/>
       <c r="B1" s="45" t="s">
         <v>78</v>
@@ -36977,7 +36962,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17">
       <c r="A2" s="45"/>
       <c r="B2" s="45" t="s">
         <v>82</v>
@@ -37028,7 +37013,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17">
       <c r="A3" s="45">
         <v>0</v>
       </c>
@@ -37081,7 +37066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17">
       <c r="A4" s="45">
         <v>1</v>
       </c>
@@ -37134,7 +37119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17">
       <c r="A5" s="45">
         <v>2</v>
       </c>
@@ -37187,7 +37172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17">
       <c r="A6" s="45">
         <v>3</v>
       </c>
@@ -37240,7 +37225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17">
       <c r="A7" s="45">
         <v>4</v>
       </c>
@@ -37293,7 +37278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17">
       <c r="A8" s="45">
         <v>5</v>
       </c>
@@ -37346,7 +37331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17">
       <c r="A9" s="45">
         <v>6</v>
       </c>
@@ -37399,7 +37384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17">
       <c r="A10" s="45">
         <v>7</v>
       </c>
@@ -37452,7 +37437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17">
       <c r="A11" s="45">
         <v>8</v>
       </c>
@@ -37505,7 +37490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17">
       <c r="A12" s="45">
         <v>9</v>
       </c>
@@ -37558,7 +37543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17">
       <c r="A13" s="45">
         <v>10</v>
       </c>
@@ -37611,7 +37596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17">
       <c r="A14" s="45">
         <v>11</v>
       </c>
@@ -37664,7 +37649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17">
       <c r="A15" s="45">
         <v>12</v>
       </c>
@@ -37717,7 +37702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17">
       <c r="A16" s="45">
         <v>13</v>
       </c>
@@ -37770,7 +37755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17">
       <c r="A17" s="45">
         <v>14</v>
       </c>
@@ -37823,7 +37808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17">
       <c r="A18" s="45">
         <v>15</v>
       </c>
@@ -37876,7 +37861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17">
       <c r="A19" s="45">
         <v>16</v>
       </c>
@@ -37929,7 +37914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17">
       <c r="A20" s="45">
         <v>17</v>
       </c>
@@ -37982,7 +37967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17">
       <c r="A21" s="45">
         <v>18</v>
       </c>
@@ -38035,7 +38020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17">
       <c r="A22" s="45">
         <v>19</v>
       </c>
@@ -38088,7 +38073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17">
       <c r="A23" s="45">
         <v>20</v>
       </c>
@@ -38150,9 +38135,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:Q23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17">
       <c r="A1" s="45"/>
       <c r="B1" s="45" t="s">
         <v>78</v>
@@ -38203,7 +38188,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17">
       <c r="A2" s="45"/>
       <c r="B2" s="45" t="s">
         <v>82</v>
@@ -38254,7 +38239,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17">
       <c r="A3" s="45">
         <v>0</v>
       </c>
@@ -38307,7 +38292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17">
       <c r="A4" s="45">
         <v>1</v>
       </c>
@@ -38360,7 +38345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17">
       <c r="A5" s="45">
         <v>2</v>
       </c>
@@ -38413,7 +38398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17">
       <c r="A6" s="45">
         <v>3</v>
       </c>
@@ -38466,7 +38451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17">
       <c r="A7" s="45">
         <v>4</v>
       </c>
@@ -38519,7 +38504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17">
       <c r="A8" s="45">
         <v>5</v>
       </c>
@@ -38572,7 +38557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17">
       <c r="A9" s="45">
         <v>6</v>
       </c>
@@ -38625,7 +38610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17">
       <c r="A10" s="45">
         <v>7</v>
       </c>
@@ -38678,7 +38663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17">
       <c r="A11" s="45">
         <v>8</v>
       </c>
@@ -38731,7 +38716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17">
       <c r="A12" s="45">
         <v>9</v>
       </c>
@@ -38784,7 +38769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17">
       <c r="A13" s="45">
         <v>10</v>
       </c>
@@ -38837,7 +38822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17">
       <c r="A14" s="45">
         <v>11</v>
       </c>
@@ -38890,7 +38875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17">
       <c r="A15" s="45">
         <v>12</v>
       </c>
@@ -38943,7 +38928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17">
       <c r="A16" s="45">
         <v>13</v>
       </c>
@@ -38996,7 +38981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17">
       <c r="A17" s="45">
         <v>14</v>
       </c>
@@ -39049,7 +39034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17">
       <c r="A18" s="45">
         <v>15</v>
       </c>
@@ -39102,7 +39087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17">
       <c r="A19" s="45">
         <v>16</v>
       </c>
@@ -39155,7 +39140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17">
       <c r="A20" s="45">
         <v>17</v>
       </c>
@@ -39208,7 +39193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17">
       <c r="A21" s="45">
         <v>18</v>
       </c>
@@ -39261,7 +39246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17">
       <c r="A22" s="45">
         <v>19</v>
       </c>
@@ -39314,7 +39299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17">
       <c r="A23" s="45">
         <v>20</v>
       </c>
